--- a/modeleLogiqueCorps/ig/FRNonHumanSubjectLMCDAFHIR.xlsx
+++ b/modeleLogiqueCorps/ig/FRNonHumanSubjectLMCDAFHIR.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T12:22:25+00:00</t>
+    <t>2026-06-30T08:22:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
